--- a/docs/qa/desk-portal-test-cases.xlsx
+++ b/docs/qa/desk-portal-test-cases.xlsx
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>POST /api/admin/users/bulk with three users, one of them invalid.</t>
+          <t>POST /api/admin/users/import with three users, one of them invalid. (users/bulk is role/activate/delete on existing users, not creation.)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -8398,17 +8398,17 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Multipart upload to Autotask</t>
+          <t>Attachment upload format per PSA</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Attach a file that must be pushed to Autotask.</t>
+          <t>Attach a file on an Autotask ticket, then on a ConnectWise ticket.</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Sent as multipart, not JSON (the real API rejects JSON with 415).</t>
+          <t>Autotask: JSON body to Tickets/{id}/Attachments with the file base64 in data. ConnectWise: multipart/form-data (its API rejects JSON with 415). Both appear in the PSA with the original file name.</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
